--- a/www/download/COUNTRY.POL.EXI382.xlsx
+++ b/www/download/COUNTRY.POL.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Polônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28097668711656</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28168159509202</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28168159509202</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28168159509202</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28168159509202</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28168159509202</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.28168159509202</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>20.244</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>15.212</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>15.417</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>15.301</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>15.185</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>14.867</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>14.953</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14.694</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>14.237</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>14.058</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>14.068</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>14.508</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>14.999</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15.648</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>15.792</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>15.859</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>15.461</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>15.556</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>15.583</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>15.458</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>15.515</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>15.915</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15.439</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16.991</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18.272</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>18.933</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>15.603</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10.762</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10.936</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>10.931</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10.927</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>10.735</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10.919</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10.653</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>10.278</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>10.315</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>10.386</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>10.817</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>11.375</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>12.015</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>12.171</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>12.251</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>11.906</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>11.998</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>12.091</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>11.852</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>11.974</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>12.488</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>11.966</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12.888</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>13.189</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>14.515</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>43271.418</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>33034.413</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>33512.747</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>33263.358</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>33013.293</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>32312.381</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>32514.121</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>31494.078</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>30762.742</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>30262.805</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>30450.534</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>31047.637</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>32115.523</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>33532.989</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>33632.068</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>33407.807</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>32532.887</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>32565.839</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>32633.862</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>32331.849</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>32443.997</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>33333.506</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>32285.007</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>35648.644</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>36205.586</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>38880.452</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>40484.612</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>33072.527</t>
+          <t>48155963922.6412</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13024.295</t>
+          <t>50258384613.9182</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13333.651</t>
+          <t>45922022207.0548</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13550.062</t>
+          <t>44299052203.3377</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13772.151</t>
+          <t>45396955094.8212</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>13578.996</t>
+          <t>44873072130.8749</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14221.017</t>
+          <t>44485707189.7988</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13589.27</t>
+          <t>42990985157.3418</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12809.316</t>
+          <t>41910049091.8499</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13178.183</t>
+          <t>42683674243.6317</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>13490.67</t>
+          <t>42923974998.0913</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>14847.515</t>
+          <t>43412754049.2422</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16177.137</t>
+          <t>44167226472.9385</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17466.637</t>
+          <t>46996773294.9818</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>17582.644</t>
+          <t>43716788338.9336</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>17682.965</t>
+          <t>44715386901.7844</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>17188.821</t>
+          <t>45319879912.5448</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17213.187</t>
+          <t>43396930867.5951</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>17386.694</t>
+          <t>43751378760.9222</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>24504.197</t>
+          <t>43820489550.5912</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>24767.304</t>
+          <t>45751538345.6745</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>25779.87</t>
+          <t>45630068164.2347</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>24658.969</t>
+          <t>43250520157.7347</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>26678.398</t>
+          <t>50375166583.2518</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>27571.841</t>
+          <t>50581681638.384</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>29518.034</t>
+          <t>55717931389.5413</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>30813.972</t>
+          <t>55581214512.6075</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10459128483.1375</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>13674596676.0515</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11590538981.2085</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10872306060.449</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10573683291.7319</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10616673765.9977</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10629637140.1993</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9581305172.82889</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8606486165.11677</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7507541571.72198</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>8327981221.95057</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>8439594657.77537</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>8647342221.2894</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10926316645.6717</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>9191952981.1291</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>9433634049.37676</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>9023765208.36956</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>9494230793.36098</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>9675828266.44453</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>9260090351.71051</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>9451033052.55154</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8532585568.15558</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>10829324768.5357</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10616342141.357</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>10403786587.4047</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11286569097.2428</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>12943863695.9478</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>51416208.4080463</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>38231717.4117131</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>29106706.9059667</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>26393401.9449976</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>27210545.9805003</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>24688503.3841615</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24024668.9230061</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22229993.5333774</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>22673409.1681916</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>20922613.1499958</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>17204080.8976802</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>39874800.5605102</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>12233963.3737644</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>11519885.3642951</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>12250311.2775477</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10547263.5945846</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>10815343.3999931</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>10314570.4975906</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>10016762.4524012</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>12618778.1952266</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>12780123.4088473</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>12660343.5076455</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>10724730.2151201</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12461111.3012392</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>11477161.6886509</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11837261.3910351</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>12137912.2622425</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>102140.272563942</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>187564.683178516</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>204055.766580816</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>205744.007807042</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>212803.892135022</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>244332.159714937</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>245212.139774671</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>227891.731460324</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>200403.661575475</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>189892.261873453</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>204125.714816253</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>221924.192895924</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>236422.890482232</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>244542.911342615</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>246463.009954724</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>277590.511767205</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>279462.006886689</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>307094.619927962</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>299952.450664091</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>306603.210041288</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>349656.558901046</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>321145.898697688</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>331100.487456841</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>363648.212309237</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>389616.899706207</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>398664.780438851</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>407703.267336757</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>179506.298323774</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>381917.104877238</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>380079.311993087</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>376938.022479124</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>407451.057109217</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>481434.820695671</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>479233.468058739</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>448939.239788632</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>402033.945740578</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>400134.765842071</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>431376.152475054</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>466700.559702577</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>491930.68833418</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>525964.836147816</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>490290.299488174</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>578320.184534057</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>610200.947168412</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>644936.940170695</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>635137.857580071</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>658457.1419836</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>776593.34371066</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>705962.760063553</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>707452.67883364</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>801391.055398204</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>857352.965398523</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>898421.389894472</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>879887.318294538</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2.16207287789972</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.0475554556719461</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.150390937093623</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.246291442187862</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.302493239111498</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.279025455552394</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.337864765506803</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.418310945625218</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.488332840400084</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.75532601106548</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.619920799585941</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.759268732926081</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.870764055130985</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.598584185907262</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.912830063002306</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.874459503881881</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.904839122371626</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.813015437969875</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.796920482797522</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.64621578781053</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.62059221912492</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2.02134324882572</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.27705507560648</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.51295574320281</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.65017364390897</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.61532394867401</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.38058530194625</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>670.315445679932</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1270.66073296765</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1059.83238978889</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>994.648704618997</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>967.709997870098</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>989.005166981569</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>973.499142797046</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>899.408158607303</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>837.369737800824</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>727.813476396198</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>801.862275602533</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>780.215832280269</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>760.185860706317</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>909.412357002204</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>755.252613335714</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>770.004574936635</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>757.891991565233</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>791.317785744059</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>800.230601047349</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>781.316754321305</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>789.284806880935</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>683.24959784594</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>905.025241049302</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>823.720249322479</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>788.800368501187</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>806.185767912108</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>891.758571362585</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1970300402.4326</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>4855536475.96752</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>1176655537.28779</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>738893982.541483</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>852083868.602643</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1308751243.63612</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>2118226270.70719</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>2032384271.98018</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1675676321.72785</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>2438486989.28795</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2965979816.67489</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>2639996016.31179</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>2103896964.40916</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>3141399635.08924</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>3326196381.0895</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>4173665382.11344</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>3768144333.79312</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>4828748182.53405</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>5493768691.09772</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>4400552213.86155</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>4563539298.80742</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>5295941132.35596</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>5385959822.85138</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>5567157988.05117</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>5794289150.79964</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>6472326469.99248</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>6206337150.64184</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3087384830.29332</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4427304125.17561</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>898945315.937503</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>462456743.39009</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>612675809.939566</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1085320977.14514</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1690378666.05939</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1626285717.51064</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1225166339.94495</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2134883429.76457</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2574185795.49234</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2295261939.07328</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1535967312.08989</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1847783614.88621</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1831069514.53309</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2846355383.66778</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2465604632.31565</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3322252037.23421</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>3743835882.72965</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2691401735.27594</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2686177812.95491</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3335665489.02772</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>3407126681.31589</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>3481516902.19559</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>3628793887.13401</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>3894115927.59762</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5193816234.73709</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-1117084427.86072</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>428232350.791911</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>277710221.350282</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>276437239.151392</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>239408058.663077</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>223430266.490977</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>427847604.647791</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>406098554.469537</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>450509981.782894</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>303603559.52338</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>391794021.182546</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>344734077.238516</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>567929652.319268</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1293616020.20303</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1495126866.55641</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1327309998.44566</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1302539701.47747</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1506496145.29984</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1749932808.36807</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1709150478.58561</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1877361485.85251</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1960275643.32823</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1978833141.53549</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2085641085.85557</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2165495263.66563</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2578210542.39486</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1012520915.90475</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>2119.58629042177</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1210.23388280693</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>1219.22157605141</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>1239.6221685499</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>1260.4357296464</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>1264.96278424227</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1302.41020239924</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>1275.64043593736</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>1246.28488032617</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>1277.54992632224</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>1298.95337865186</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>1372.60931866458</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>1422.12838342819</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>1453.77221237237</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>1444.66990394961</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1443.3423935225</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>1443.6623160656</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>1434.67136189412</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>1437.95075798335</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2067.53273056592</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>2068.39362358569</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>2064.33155971472</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>2060.79231868329</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>2069.97253132737</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>2090.45794690753</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>2108.43694590068</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1.116</t>
+          <t>2122.90734787035</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2137.53563392417</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>2171.54512108494</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>2173.73870572309</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>2173.90518390707</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>2174.07263747091</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2173.47366934149</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>2174.42125326009</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>2143.3437004468</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2160.79048662586</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>2152.77181026646</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2164.47857950162</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>2140.00613446164</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>2141.10623687596</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>2142.92947431617</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>2129.7171949996</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>2106.59177612271</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>2104.13591266072</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>2093.44495085518</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>2094.23668555496</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>2091.56569931453</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>2091.0824402363</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>2094.43256391625</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>2091.07738896913</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>2098.06433026575</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>2114.79168508135</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>2127.87374422137</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>2138.29394369429</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>32064.5373290125</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>29351.9281082745</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>34784.6995226392</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>44246.8253283201</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>41676.1937099903</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>57006.6243901487</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>66420.6858341813</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>68316.7655071152</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>70480.9993185274</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>74483.3607268565</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>92163.0458591761</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>110135.496365419</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>124407.820422001</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>139241.085079751</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>123141.48634838</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>153731.47167956</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>169408.153563172</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>185234.883892708</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>193570.473493773</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>206674.323767528</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>234014.878940455</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>247280.719229674</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>281783.263354992</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>303990.690319025</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>331234.813941572</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>350340.924909892</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>367265.321861204</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4174699917.30232</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5550597813.5635</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>5446702458.8234</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6032868750.31684</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>5672182521.28975</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6251628927.89039</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6560478211.38491</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6707677653.8101</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7166454199.98063</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>7231066172.76283</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>7592529001.86897</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>7860948387.03973</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7627972836.28694</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>7743515118.95665</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>7778565289.38413</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>8398890026.05706</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>8773076912.7639</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>8950994547.21623</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>9574994930.88711</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>10302274794.0409</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>11053642185.0749</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>12128353906.6002</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>12382686626.884</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14769582511.6144</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>15545081467.0893</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17479264394.4947</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>17412709196.1223</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>28990.2896576943</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>31685.3785147159</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>41914.7043359497</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>54114.8916899585</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>54045.7771163709</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>72840.3252154127</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>76965.6757350015</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>78122.8339662212</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>77395.7373034888</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>82463.1909305054</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>96371.1169580652</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>118496.127373678</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>139962.552813726</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>164277.743628862</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>127196.250763117</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>164009.592330766</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>180144.495353466</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>189103.858426745</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>186176.386139214</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>201499.825483256</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>218489.678294689</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>226232.017690716</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>258816.206717998</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>284065.744547223</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>298467.106247231</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>319456.768692167</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>336865.67560022</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>43271.418</t>
+          <t>4403358346.60148</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33034.413</t>
+          <t>10880146852.1066</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33512.747</t>
+          <t>7958007320.64444</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>33263.358</t>
+          <t>8630889862.23509</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>33013.293</t>
+          <t>8793390922.9692</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>32312.381</t>
+          <t>10016829675.4693</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>32514.121</t>
+          <t>10379389787.6522</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>31494.078</t>
+          <t>10380946179.931</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>30762.742</t>
+          <t>10016790010.0091</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>30262.805</t>
+          <t>11132972959.4893</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>30450.534</t>
+          <t>11262311168.6793</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>31047.637</t>
+          <t>11744936900.7494</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>32115.523</t>
+          <t>11663493862.958</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>33532.989</t>
+          <t>14315922153.9467</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>33632.068</t>
+          <t>11701588161.8331</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>33407.807</t>
+          <t>13839868409.11</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>32532.887</t>
+          <t>13779290609.3387</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>32565.839</t>
+          <t>14201581788.0125</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>32633.862</t>
+          <t>14221744616.1706</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>32331.849</t>
+          <t>14152746314.4384</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>32443.997</t>
+          <t>14116439773.6633</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>33333.506</t>
+          <t>15191942756.0825</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>32285.007</t>
+          <t>15556396233.7554</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>35648.644</t>
+          <t>18356405994.2539</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>36205.586</t>
+          <t>18348746932.8629</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>38880.452</t>
+          <t>20954551379.5354</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>40484.612</t>
+          <t>20657054564.1793</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>33072.527</t>
+          <t>3074.24767131819</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13024.295</t>
+          <t>-2333.45040644144</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13333.651</t>
+          <t>-7130.00481331054</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13550.062</t>
+          <t>-9868.06636163837</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13772.151</t>
+          <t>-12369.5834063806</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13578.996</t>
+          <t>-15833.700825264</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14221.017</t>
+          <t>-10544.9899008202</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13589.27</t>
+          <t>-9806.06845910598</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>12809.316</t>
+          <t>-6914.73798496142</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13178.183</t>
+          <t>-7979.8302036489</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>13490.67</t>
+          <t>-4208.07109888907</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>14847.515</t>
+          <t>-8360.63100825853</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>16177.137</t>
+          <t>-15554.732391725</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>17466.637</t>
+          <t>-25036.6585491114</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17582.644</t>
+          <t>-4054.76441473642</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>17682.965</t>
+          <t>-10278.1206512064</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>17188.821</t>
+          <t>-10736.3417902943</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>17213.187</t>
+          <t>-3868.97453403767</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>17386.694</t>
+          <t>7394.08735455871</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>24504.197</t>
+          <t>5174.4982842724</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>24767.304</t>
+          <t>15525.2006457666</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>25779.87</t>
+          <t>21048.701538958</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>24658.969</t>
+          <t>22967.0566369936</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>26678.398</t>
+          <t>19924.9457718011</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>27571.841</t>
+          <t>32767.7076943408</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>29518.034</t>
+          <t>30884.156217725</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>30813.972</t>
+          <t>30399.646260984</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>45233.09</t>
+          <t>-228658429.299163</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45498.657</t>
+          <t>-5329549038.54306</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42283.828</t>
+          <t>-2511304861.82104</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40886.052</t>
+          <t>-2598021111.91825</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>41616.281</t>
+          <t>-3121208401.67945</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>40757.169</t>
+          <t>-3765200747.5789</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40467.314</t>
+          <t>-3818911576.26727</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>39058.97</t>
+          <t>-3673268526.12092</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>38025.489</t>
+          <t>-2850335810.02852</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>38560.054</t>
+          <t>-3901906786.72647</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>38719.387</t>
+          <t>-3669782166.81038</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>39141.108</t>
+          <t>-3883988513.7097</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>40014.891</t>
+          <t>-4035521026.67102</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>42277.715</t>
+          <t>-6572407034.99004</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>39816.802</t>
+          <t>-3923022872.44895</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>40363.539</t>
+          <t>-5440978383.05294</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>40722.006</t>
+          <t>-5006213696.5748</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>39119.432</t>
+          <t>-5250587240.79624</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>39376.539</t>
+          <t>-4646749685.28345</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>39383.984</t>
+          <t>-3850471520.39756</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>41051.386</t>
+          <t>-3062797588.58836</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>40795.76</t>
+          <t>-3063588849.48228</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>38877.128</t>
+          <t>-3173709606.87132</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>45086.56</t>
+          <t>-3586823482.63954</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>45264.628</t>
+          <t>-2803665465.77363</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>49623.251</t>
+          <t>-3475286985.0407</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>49676.155</t>
+          <t>-3244345368.05698</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>51592.0255856444</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>57938.3086287194</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>61442.3514594325</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>67252.3562533547</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>65335.5704363784</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>74708.0543571663</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>84904.7568275121</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>82093.967035212</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>72180.8694038458</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>70216.5988087275</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>89282.3909270335</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>100844.485185738</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>114590.53222295</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>142359.293707159</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>111667.142699121</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>131231.973905264</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>137345.468441166</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>136990.682185016</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>137526.963628298</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>147564.447643294</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>151950.761052382</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>145443.151371052</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>167600.943863664</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>174833.127258601</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>185460.232891023</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>195109.224744816</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.657</t>
+          <t>201781.053502645</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>27401.062</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>24682.576</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>24654.469</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>24179.743</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>23709.961</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>22773.456</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>22762.257</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>21823.198</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>20891.09</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>20256.424</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>20311.478</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>20643.516</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>21226.859</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>21850.753</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>21975.901</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>21463.14</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>20755.76</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>20663.98</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>20662.181</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>20404.521</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>20599.359</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>20757.34</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>20242.016</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>22858.802</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>22986.423</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>24724.23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>25754.028</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>66034.3504430648</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>76052.7656096203</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>81223.4903431497</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>89144.0809847166</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>89150.8215310345</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>103918.465909051</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>122078.848503083</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>118695.566704202</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>101642.99845011</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>99665.7864001936</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>123095.499466174</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>137814.561683939</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>153542.650312249</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>198646.289751843</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>160125.444579735</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>186658.992726774</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>196234.850823623</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>198580.188645348</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>198472.662529531</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>209508.2648537</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>220612.43078019</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>208022.534125541</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>241484.296828035</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>245713.886855137</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>263847.346395346</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>276908.953705836</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>290581.706684615</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>9798.675</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>12132.55</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>10598.05</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>9983.907</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>9613.877</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>9573.26</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>9566.698</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>8590.976</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>7792.839</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>6731.632</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>7521.258</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>7580.94</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>7820.775</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>9797.03</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>8281.739</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>8457.785</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>7970.451</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>8389.584</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>8559.518</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>8224.183</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>8292.897</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>7578.292</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>9631.004</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>9370.688</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>9247.179</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>9787.407</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>11403.567</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>237.52</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>7.35</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>25.81</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>35.72</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>41.84</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>58.18</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>64.37</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>95.77</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>79.37</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>95.85</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>106.85</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>78.29</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>112.31</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>109.07</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>115.66</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>105.17</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>103.13</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>197.95</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>198.66</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>240.18</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>156.04</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>184.7</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>198.16</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>201.59</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>170.21</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>63.812</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>45.641</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>35.369</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>32.014</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>32.839</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>28.939</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>28.556</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>25.977</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>26.482</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>24.522</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>20.217</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>48.638</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>14.465</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>13.357</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>14.272</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>12.255</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>12.379</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>11.793</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>11.491</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>14.552</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>14.768</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>14.521</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>12.426</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14.405</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>13.261</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13.685</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>13.998</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>65366.4647207084</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>75822.2640420764</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>88789.1169212896</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>100075.809965843</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>104707.234798684</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>123382.152093178</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>137937.845523581</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>134726.623054746</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>131438.322534927</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>148957.903380562</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>174696.940048067</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>190654.926410666</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>222422.743015239</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>236105.777148434</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>220858.719850573</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>250639.38197666</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>261667.801513545</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>269975.232294796</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>274779.073992609</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>280965.587204516</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>297669.059720146</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>305903.600923424</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>317649.68094114</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>351730.83987051</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>376716.365204083</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>384457.194631543</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>387927.049983187</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>33072526502.9976</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>13024294999.9918</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13333651000.0127</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>13550061999.9849</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>13772150999.987</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>13578996000.0064</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14221016999.9951</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13589269999.9987</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>12809315999.9923</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>13178182999.999</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>13490669999.9989</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>14847514999.9942</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>16177137000.0047</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>17466636999.9861</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>17582644000.0074</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17682964999.998</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>17188820999.9983</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>17213187000.0124</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>17386694000.0054</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>24504197285.2483</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>24767303680.209</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>25779869801.3746</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>24658968929.5853</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>26678397955.929</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>27571841010.7937</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>29518034458.383</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>30813971664.9689</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>43271417699.8908</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>33034412999.9904</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>33512747000.0012</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>33263357999.9992</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>33013293000.0023</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>32312381000.0046</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>32514120999.994</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>31494077999.9953</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>30762741999.9961</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>30262805000.0019</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>30450533999.9963</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>31047636999.9986</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>32115523000.0095</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>33532988999.9889</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>33632068000.0038</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>33407806999.9944</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>32532887000.0099</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>32565839000.0044</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>32633861999.9983</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>32331849071.6698</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>32443997017.7018</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>33333505860.4451</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>32285007436.9303</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>35648644424.0861</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>36205585659.0533</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>38880452247.4661</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>40484611922.2429</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>27401062394.848</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>24682576053.2607</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>24654468550.9541</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>24179743084.6151</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>23709961151.6464</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>22773455835.4918</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>22762257180.3834</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>21823198278.0218</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>20891089878.8488</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>20256423932.9105</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>20311477648.8416</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>20643515855.021</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>21226858976.1611</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>21850753083.4891</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>21975901319.7182</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>21463140083.7851</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>20755760296.6617</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>20663979934.6847</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>20662180852.0003</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>20404521274.2588</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>20599359487.0909</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>20757340297.8377</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>20242015806.0569</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>22858801766.4822</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>22986423068.7217</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>24724229781.0024</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>25754028144.4876</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20243600.6273502</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>15212399.999999</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>15417099.9999989</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>15301200.0000001</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15185000.000003</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>14866700.0000025</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14952999.9999981</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>14693900.0000001</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>14236800.0000005</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>14057600</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>14068299.9999971</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>14508200.0000011</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>14999499.9999946</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>15648199.9999975</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>15791800.0000043</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>15858699.9999987</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>15461399.9999988</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>15556100.0000029</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>15582700.0000005</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>15458203.910241</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>15515407.9023472</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>15915292.0149966</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>15439413.0065393</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16991206.5658971</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>17120166.4516004</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18271973.3034223</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>18933136.8784118</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>15603293.2711678</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10761800.0000002</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10936199.9999994</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10930799.9999997</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10926500.0000044</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>10734700.0000007</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10918999.9999983</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>10652900.0000013</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>10277999.9999999</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10315199.9999999</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10385799.9999972</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>10816999.9999996</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>11375299.9999958</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12014699.9999971</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12170700.0000055</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>12251399.9999975</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>11906399.9999964</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>11998000.0000048</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>12091300.0000009</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>11851902.9580446</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>11974173.2897403</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>12488240.8933075</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>11965770.9833375</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12888285.9806944</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>13189378.4572808</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13999960.7366838</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>14514986.5800223</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>43271417699.8908</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>33034412999.9904</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>33512747000.0012</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>33263357999.9992</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>33013293000.0023</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>32312381000.0046</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>32514120999.994</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>31494077999.9953</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>30762741999.9961</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>30262805000.0019</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>30450533999.9963</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>31047636999.9986</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>32115523000.0095</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>33532988999.9889</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>33632068000.0038</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>33407806999.9944</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>32532887000.0099</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>32565839000.0044</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>32633861999.9983</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>32331849071.6698</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>32443997017.7018</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>33333505860.4451</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>32285007436.9303</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>35648644424.0861</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>36205585659.0533</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>38880452247.4661</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>40484611922.2429</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>33072526502.9976</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>13024294999.9918</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13333651000.0127</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13550061999.9849</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>13772150999.987</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>13578996000.0064</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14221016999.9951</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>13589269999.9987</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>12809315999.9923</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>13178182999.999</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>13490669999.9989</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>14847514999.9942</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16177137000.0047</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>17466636999.9861</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>17582644000.0074</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>17682964999.998</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>17188820999.9983</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>17213187000.0124</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>17386694000.0054</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>24504197285.2483</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>24767303680.209</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>25779869801.3746</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>24658968929.5853</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>26678397955.929</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>27571841010.7937</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>29518034458.383</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30813971664.9689</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>263883.648437202</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>301966.83163846</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>336678.358411154</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>372547.019343711</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>382138.632520686</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>455903.552703838</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>523860.966222264</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>518602.67654356</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>481124.890241945</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>513907.040150566</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>617213.044302263</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>710828.094301578</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>819081.502562303</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>950436.465124634</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>776904.64154423</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>915734.418810048</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>971658.532718555</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>991521.163760537</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>997574.736511539</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1031592.33182184</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1091845.31147809</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1088841.67054965</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1183524.38473094</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1270886.50438977</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1360565.19179499</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1417436.25962034</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1438564.24017073</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>74520.0119086385</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>86519.7434401108</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>92294.8740842175</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>100908.744711348</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>101157.099648326</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>117639.982468038</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>137796.577865996</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>137677.51466733</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>117773.377430556</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>116069.585001564</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>143339.951116322</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>164057.782501511</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>182079.523133694</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>232944.818156171</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>186711.785289677</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>217166.630240699</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>228656.693551897</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>231264.328503148</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>232362.778336248</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>247035.397957675</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>258915.364300976</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>247788.384197679</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>285571.327935213</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>292806.705642847</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>313513.634719272</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>327415.463563197</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>342695.324682101</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
